--- a/src/test/resources/packages_qa.xlsx
+++ b/src/test/resources/packages_qa.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B130F1-7EDF-4D04-9CFB-9A6D831DD735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841CC830-2941-4331-94FC-3F4CD98FFF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{75A6ABCC-9875-48AC-9A16-7CDC4958549E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{75A6ABCC-9875-48AC-9A16-7CDC4958549E}"/>
   </bookViews>
   <sheets>
     <sheet name="Packages" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
   <si>
     <t>PackageType</t>
   </si>
@@ -66,19 +66,47 @@
     <t>CO</t>
   </si>
   <si>
-    <t>CO-25-9037</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
     <t>NY-25-9034</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>MD-25-9543</t>
+  </si>
+  <si>
+    <t>MD-25-9544</t>
+  </si>
+  <si>
+    <t>MD-25-9545</t>
+  </si>
+  <si>
+    <t>MD-25-9546</t>
+  </si>
+  <si>
+    <t>MD-25-9547</t>
+  </si>
+  <si>
+    <t>CO-25-9040</t>
+  </si>
+  <si>
+    <t>MD-25-9548</t>
+  </si>
+  <si>
+    <t>MD-25-9549</t>
+  </si>
+  <si>
+    <t>CO-25-9045</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -455,16 +483,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5CF9F-A3EF-4F4C-99C9-E52FA1956C25}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="26.28515625"/>
+    <col min="2" max="2" customWidth="true" width="16.7109375"/>
+    <col min="3" max="3" customWidth="true" width="13.5703125"/>
+    <col min="4" max="4" customWidth="true" width="27.140625"/>
+    <col min="5" max="5" customWidth="true" width="20.7109375"/>
+    <col min="6" max="6" customWidth="true" width="26.42578125"/>
+    <col min="7" max="7" customWidth="true" width="30.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -491,71 +519,255 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="C10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s" s="0">
         <v>10</v>
       </c>
     </row>

--- a/src/test/resources/packages_qa.xlsx
+++ b/src/test/resources/packages_qa.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="50">
   <si>
     <t>PackageType</t>
   </si>
@@ -100,6 +100,81 @@
   </si>
   <si>
     <t>CO-25-9045</t>
+  </si>
+  <si>
+    <t>CO-25-9046</t>
+  </si>
+  <si>
+    <t>CO-25-9047</t>
+  </si>
+  <si>
+    <t>CO-25-9048</t>
+  </si>
+  <si>
+    <t>CO-25-9049</t>
+  </si>
+  <si>
+    <t>CO-25-9050</t>
+  </si>
+  <si>
+    <t>CO-25-9051</t>
+  </si>
+  <si>
+    <t>CO-25-9053</t>
+  </si>
+  <si>
+    <t>CO-25-9054</t>
+  </si>
+  <si>
+    <t>CO-25-9055</t>
+  </si>
+  <si>
+    <t>CO-25-9056</t>
+  </si>
+  <si>
+    <t>CO-25-9057</t>
+  </si>
+  <si>
+    <t>CO-25-9058</t>
+  </si>
+  <si>
+    <t>CO-25-9059</t>
+  </si>
+  <si>
+    <t>CO-25-9060</t>
+  </si>
+  <si>
+    <t>CO-25-9061</t>
+  </si>
+  <si>
+    <t>CO-25-9062</t>
+  </si>
+  <si>
+    <t>CO-25-9063</t>
+  </si>
+  <si>
+    <t>CO-25-9064</t>
+  </si>
+  <si>
+    <t>CO-25-9065</t>
+  </si>
+  <si>
+    <t>CO-25-9066</t>
+  </si>
+  <si>
+    <t>CO-25-9067</t>
+  </si>
+  <si>
+    <t>CO-25-9068</t>
+  </si>
+  <si>
+    <t>CO-25-9069</t>
+  </si>
+  <si>
+    <t>CO-25-9070</t>
+  </si>
+  <si>
+    <t>CO-25-9071</t>
   </si>
 </sst>
 </file>
@@ -483,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5CF9F-A3EF-4F4C-99C9-E52FA1956C25}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="26.28515625"/>
@@ -771,6 +846,581 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/packages_qa.xlsx
+++ b/src/test/resources/packages_qa.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="58">
   <si>
     <t>PackageType</t>
   </si>
@@ -175,6 +175,30 @@
   </si>
   <si>
     <t>CO-25-9071</t>
+  </si>
+  <si>
+    <t>CO-25-9072</t>
+  </si>
+  <si>
+    <t>CO-25-9073</t>
+  </si>
+  <si>
+    <t>CO-25-9074</t>
+  </si>
+  <si>
+    <t>CO-25-9075</t>
+  </si>
+  <si>
+    <t>CO-25-9076</t>
+  </si>
+  <si>
+    <t>CO-25-9077</t>
+  </si>
+  <si>
+    <t>CO-25-9078</t>
+  </si>
+  <si>
+    <t>CO-25-9079</t>
   </si>
 </sst>
 </file>
@@ -558,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5CF9F-A3EF-4F4C-99C9-E52FA1956C25}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="26.28515625"/>
@@ -1421,6 +1445,190 @@
         <v>10</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F44" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/packages_qa.xlsx
+++ b/src/test/resources/packages_qa.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="59">
   <si>
     <t>PackageType</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>CO-25-9079</t>
+  </si>
+  <si>
+    <t>CO-25-9080</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A5CF9F-A3EF-4F4C-99C9-E52FA1956C25}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="26.28515625"/>
@@ -1629,6 +1632,29 @@
         <v>10</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
